--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.00078876516301</v>
+        <v>5.037628174338989</v>
       </c>
       <c r="D2" t="n">
-        <v>24.20355529439608</v>
+        <v>3.933077735339362</v>
       </c>
       <c r="E2" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F2" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.72810650139792</v>
+        <v>2.393317306477163</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6182108648387</v>
+        <v>2.375459265536289</v>
       </c>
       <c r="E3" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F3" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.66632018867543</v>
+        <v>1.408277030659757</v>
       </c>
       <c r="D4" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E4" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F4" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.03404732705267</v>
+        <v>4.068032690646058</v>
       </c>
       <c r="D5" t="n">
-        <v>25.0957350758763</v>
+        <v>4.078056949829898</v>
       </c>
       <c r="E5" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F5" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.68651583643652</v>
+        <v>4.824058823420935</v>
       </c>
       <c r="D6" t="n">
-        <v>29.75908187533556</v>
+        <v>4.835850804742028</v>
       </c>
       <c r="E6" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F6" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.59144224010798</v>
+        <v>6.596109364017547</v>
       </c>
       <c r="D7" t="n">
-        <v>30.5319004394493</v>
+        <v>4.961433821410512</v>
       </c>
       <c r="E7" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F7" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.27713837783665</v>
+        <v>4.595034986398455</v>
       </c>
       <c r="D8" t="n">
-        <v>28.00673526109217</v>
+        <v>4.551094479927478</v>
       </c>
       <c r="E8" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F8" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.15499009378069</v>
+        <v>5.712685890239363</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61984672551333</v>
+        <v>5.625725092895917</v>
       </c>
       <c r="E9" t="n">
-        <v>9.782964569921383</v>
+        <v>1.589731742612225</v>
       </c>
       <c r="F9" t="n">
-        <v>9.150616537979696</v>
+        <v>1.4869751874217</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
